--- a/output/pdf_financials_xlsx/GRC.xlsx
+++ b/output/pdf_financials_xlsx/GRC.xlsx
@@ -5991,7 +5991,7 @@
         <v>-1.976574</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>2.591479</v>
+        <v>-2.591479</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-11.803798</v>
@@ -22807,7 +22807,7 @@
         </is>
       </c>
       <c r="N160" s="5" t="n">
-        <v>2.591479</v>
+        <v>-2.591479</v>
       </c>
       <c r="O160" s="5" t="n">
         <v>-11.803798</v>

--- a/output/pdf_financials_xlsx/GRC.xlsx
+++ b/output/pdf_financials_xlsx/GRC.xlsx
@@ -8510,7 +8510,11 @@
           <t>Reclamation deposit 5</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -10234,7 +10238,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11468,7 +11476,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -19500,7 +19512,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -24162,7 +24178,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GRC.xlsx
+++ b/output/pdf_financials_xlsx/GRC.xlsx
@@ -728,52 +728,52 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.523657</v>
+        <v>0.594207</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.626248</v>
+        <v>1.725498</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.003379</v>
+        <v>3.289756</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3.108893</v>
+        <v>3.466209</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.926135</v>
+        <v>1.108288</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.645398</v>
+        <v>0.771406</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.456854</v>
+        <v>0.570338</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.453695</v>
+        <v>0.510983</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.304854</v>
+        <v>0.374154</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.301635</v>
+        <v>0.36141</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.213908</v>
+        <v>0.266756</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.364123</v>
+        <v>0.429239</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.381377</v>
+        <v>0.43212</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.318999</v>
+        <v>0.36271</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.311419</v>
+        <v>0.355433</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.28327</v>
+        <v>0.331832</v>
       </c>
     </row>
     <row r="8">
@@ -926,19 +926,19 @@
         <v>1.577994</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.371369</v>
+        <v>0.436485</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.381377</v>
+        <v>0.43212</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.318999</v>
+        <v>0.36271</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.311419</v>
+        <v>0.355433</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.28327</v>
+        <v>0.331832</v>
       </c>
     </row>
     <row r="11">
@@ -983,19 +983,19 @@
         <v>-1.577994</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.371369</v>
+        <v>-0.436485</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.381377</v>
+        <v>-0.43212</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.318999</v>
+        <v>-0.36271</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.311419</v>
+        <v>-0.355433</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.28327</v>
+        <v>-0.331832</v>
       </c>
     </row>
     <row r="12">
@@ -6624,43 +6624,43 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.08608</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.017363</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.30328</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.09800300000000001</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.018137</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012588</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.020451</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.033269</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.039161</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001483</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.23759</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.163736</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -7925,43 +7925,43 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.08608</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.017363</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.30328</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.09800300000000001</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.018137</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012588</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.020451</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.033269</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.039161</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001483</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.23759</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.163736</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -7980,16 +7980,16 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.07996</v>
+        <v>-1.16604</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.476213</v>
+        <v>-2.493576</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-5.52029</v>
+        <v>-5.82357</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-7.066047</v>
+        <v>-7.16405</v>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
@@ -8002,25 +8002,25 @@
         </is>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-2.0453</v>
+        <v>-2.065751</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-1.591764</v>
+        <v>-1.625033</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-1.932538</v>
+        <v>-1.971699</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1.110454</v>
+        <v>-1.111937</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-1.327228</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-0.942336</v>
+        <v>-1.179926</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-0.427422</v>
+        <v>-0.591158</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-0.408863</v>
@@ -20978,7 +20978,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -21460,7 +21464,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -24374,7 +24382,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -24664,7 +24676,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -30182,7 +30198,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E239" s="5" t="n">
         <v>-0.08608</v>
       </c>
@@ -31458,7 +31478,11 @@
           <t>Directors’ fees 10</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -35326,7 +35350,11 @@
           <t>Directors’ fees 13</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -36732,7 +36760,11 @@
           <t>Directors’ fees 11</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -40014,7 +40046,11 @@
           <t>Directors’ fees 14</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -41152,7 +41188,11 @@
           <t>Directors’ fees 15</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -44180,7 +44220,11 @@
           <t>Directors’ fees 12</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -44846,7 +44890,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E396" s="5" t="n">
         <v>0.07055</v>
       </c>
